--- a/株式会社やる気スイッチグループ_LINEOA施策提案【SIM】_ver3.00.xlsx
+++ b/株式会社やる気スイッチグループ_LINEOA施策提案【SIM】_ver3.00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC261AD-2B3B-403B-A740-E9BD684E6BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E7F587-67AB-4332-BFCB-887463B7CF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SIM2_チャイルドアイズ" sheetId="1" r:id="rId1"/>
@@ -2060,7 +2060,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="122">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>22</v>
@@ -2247,31 +2247,31 @@
       <c r="C16" s="96"/>
       <c r="D16" s="42">
         <f>H10</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -3832,27 +3832,27 @@
       </c>
       <c r="E55" s="27">
         <f t="shared" ref="E55:J55" si="17">SUM(E65:E72)+E54</f>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" si="17"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="17"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="17"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="17"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="17"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
@@ -3904,27 +3904,27 @@
       </c>
       <c r="E57" s="28">
         <f t="shared" ref="E57:J57" si="19">+E61/E35</f>
-        <v>122.30803385343812</v>
+        <v>428.07811848703341</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" si="19"/>
-        <v>62.721865045372851</v>
+        <v>219.52652765880498</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="19"/>
-        <v>42.430786750511849</v>
+        <v>148.50775362679147</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="19"/>
-        <v>80.539115952647251</v>
+        <v>181.2130108934563</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="19"/>
-        <v>65.182755388900901</v>
+        <v>146.66119962502702</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="19"/>
-        <v>54.948297837643018</v>
+        <v>123.63367013469679</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -3974,27 +3974,27 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f t="shared" ref="E59:J59" si="21">+IFERROR(E55/E40,0)</f>
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" si="21"/>
-        <v>5000</v>
+        <v>17500</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="21"/>
-        <v>2857.1428571428573</v>
+        <v>10000</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="21"/>
-        <v>4444.4444444444443</v>
+        <v>10000</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="21"/>
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="21"/>
-        <v>3333.3333333333335</v>
+        <v>7500</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -4027,27 +4027,27 @@
       </c>
       <c r="E61" s="40">
         <f t="shared" ref="E61:J61" si="22">+SUM(E65:E72)+E54</f>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" si="22"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="22"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="22"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="22"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="22"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -4259,22 +4259,22 @@
         <v>0</v>
       </c>
       <c r="E70" s="51">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="F70" s="51">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G70" s="51">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H70" s="51">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I70" s="51">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J70" s="51">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N70" s="67" t="s">
         <v>125</v>
@@ -4357,27 +4357,27 @@
       </c>
       <c r="E73" s="111">
         <f>SUM(E65:E72)</f>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="F73" s="111">
         <f t="shared" ref="D73:J73" si="26">SUM(F65:F72)</f>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="G73" s="111">
         <f t="shared" si="26"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="H73" s="111">
         <f t="shared" si="26"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="I73" s="111">
         <f t="shared" si="26"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="J73" s="111">
         <f t="shared" si="26"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -4678,7 +4678,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="122">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>22</v>
@@ -4865,31 +4865,31 @@
       <c r="C16" s="96"/>
       <c r="D16" s="42">
         <f>H10</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -6450,27 +6450,27 @@
       </c>
       <c r="E55" s="27">
         <f t="shared" ref="E55:J55" si="17">SUM(E65:E72)+E54</f>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" si="17"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="17"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="17"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="17"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="17"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
@@ -6522,27 +6522,27 @@
       </c>
       <c r="E57" s="28">
         <f t="shared" ref="E57:J57" si="19">+E61/E35</f>
-        <v>142.20675197248224</v>
+        <v>497.72363190368782</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" si="19"/>
-        <v>73.090306356901095</v>
+        <v>255.81607224915385</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="19"/>
-        <v>49.482663998467181</v>
+        <v>173.18932399463515</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="19"/>
-        <v>93.960325208211628</v>
+        <v>211.41073171847614</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="19"/>
-        <v>76.062239038193468</v>
+        <v>171.14003783593529</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="19"/>
-        <v>64.129182526061911</v>
+        <v>144.29066068363929</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
@@ -6592,27 +6592,27 @@
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f t="shared" ref="E59:J59" si="21">+IFERROR(E55/E40,0)</f>
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" si="21"/>
-        <v>5000</v>
+        <v>17500</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="21"/>
-        <v>3333.3333333333335</v>
+        <v>11666.666666666666</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="21"/>
-        <v>5000</v>
+        <v>11250</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="21"/>
-        <v>3636.3636363636365</v>
+        <v>8181.818181818182</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="21"/>
-        <v>3076.9230769230771</v>
+        <v>6923.0769230769229</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
@@ -6645,27 +6645,27 @@
       </c>
       <c r="E61" s="40">
         <f t="shared" ref="E61:J61" si="22">+SUM(E65:E72)+E54</f>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" si="22"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="22"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="22"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="22"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="22"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -6877,22 +6877,22 @@
         <v>0</v>
       </c>
       <c r="E70" s="28">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="F70" s="28">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="G70" s="28">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H70" s="28">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I70" s="28">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="J70" s="28">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="N70" s="67" t="s">
         <v>125</v>
@@ -6975,27 +6975,27 @@
       </c>
       <c r="E73" s="111">
         <f t="shared" si="25"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="F73" s="111">
         <f t="shared" si="25"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="G73" s="111">
         <f t="shared" si="25"/>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="H73" s="111">
         <f t="shared" si="25"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="I73" s="111">
         <f t="shared" si="25"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="J73" s="111">
         <f t="shared" si="25"/>
-        <v>40000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -7189,11 +7189,11 @@
       </c>
       <c r="D5" s="28">
         <f>+SIM1_忍者ナイン!G61</f>
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="E5" s="28">
         <f>+SIM1_忍者ナイン!J61</f>
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -7330,11 +7330,11 @@
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
-        <v>49.482663998467181</v>
+        <v>173.18932399463515</v>
       </c>
       <c r="E13" s="28">
         <f>+E5/E11</f>
-        <v>64.129182526061911</v>
+        <v>144.29066068363929</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -7356,15 +7356,15 @@
       <c r="B15" s="7"/>
       <c r="C15" s="84">
         <f>+SIM1_忍者ナイン!D16</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D15" s="84">
         <f>+SIM1_忍者ナイン!E16</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="84">
         <f>+SIM1_忍者ナイン!F16</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="84"/>
       <c r="R15" s="5" t="s">
@@ -7576,11 +7576,11 @@
       </c>
       <c r="D23" s="87">
         <f>+IFERROR(D5/D16,"--")</f>
-        <v>3333.3333333333335</v>
+        <v>11666.666666666666</v>
       </c>
       <c r="E23" s="87">
         <f>+IFERROR(E5/E16,"--")</f>
-        <v>3076.9230769230771</v>
+        <v>6923.0769230769229</v>
       </c>
       <c r="F23" s="87"/>
       <c r="R23" s="34"/>
